--- a/offers/seasonal/عروض اليوم الوطني انستيزيا.xlsx
+++ b/offers/seasonal/عروض اليوم الوطني انستيزيا.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E72EE1-1FDF-4973-849E-42450625C41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DA5DE5-2B5B-4950-8693-9FD740686125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="28">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -49,115 +49,58 @@
     <t>كمية</t>
   </si>
   <si>
-    <t>00045691</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية اديكت (اماريللو) 834533</t>
   </si>
   <si>
-    <t>00045692</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية اديكت (بلو) 835196</t>
   </si>
   <si>
-    <t>00045689</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية اديكت (تيرا) 699989</t>
   </si>
   <si>
-    <t>00045687</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية اديكت (جريجير) 699965</t>
   </si>
   <si>
-    <t>00045690</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية اديكت (سيليست) 699996</t>
   </si>
   <si>
-    <t>00045688</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية اديكت (نوكيولا) 699972</t>
   </si>
   <si>
-    <t>00045703</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (اديكت ارينا) 364478</t>
   </si>
   <si>
-    <t>00045700</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (اديكت اورو) 834861</t>
   </si>
   <si>
-    <t>00045698</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (اديكت ايوليت) 365138</t>
   </si>
   <si>
-    <t>00045702</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (اديكت جراي) 2219/833543</t>
   </si>
   <si>
-    <t>00045696</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (اديكت مارون) 833871</t>
   </si>
   <si>
-    <t>00045699</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (اديكت نيفي) 365796</t>
   </si>
   <si>
-    <t>00045697</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (انستاتيك نان) 363158</t>
   </si>
   <si>
-    <t>00046796</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (برونز) 810963</t>
   </si>
   <si>
-    <t>00047606</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (سابلير) 819911</t>
   </si>
   <si>
-    <t>00045693</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (فيجاس جراي) 831235</t>
   </si>
   <si>
-    <t>00045701</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (لا فانيليا) 830900</t>
   </si>
   <si>
-    <t>00045694</t>
-  </si>
-  <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (لاسينامون) 831563</t>
-  </si>
-  <si>
-    <t>00045695</t>
   </si>
   <si>
     <t>انستيزيا عدسات لاصقة شهرية دريم (لاموكا) 832553</t>
@@ -225,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -244,6 +187,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,11 +563,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="8">
+        <v>45691</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C2" s="3">
         <v>98</v>
@@ -642,11 +586,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
+      <c r="A3" s="8">
+        <v>45692</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
         <v>98</v>
@@ -665,11 +609,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
+      <c r="A4" s="8">
+        <v>45689</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3">
         <v>98</v>
@@ -688,11 +632,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
+      <c r="A5" s="8">
+        <v>45687</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3">
         <v>98</v>
@@ -711,11 +655,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" s="8">
+        <v>45690</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3">
         <v>98</v>
@@ -734,11 +678,11 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
+      <c r="A7" s="8">
+        <v>45688</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3">
         <v>98</v>
@@ -757,11 +701,11 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
+      <c r="A8" s="8">
+        <v>45703</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3">
         <v>98</v>
@@ -780,11 +724,11 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
+      <c r="A9" s="8">
+        <v>45700</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3">
         <v>98</v>
@@ -803,11 +747,11 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>25</v>
+      <c r="A10" s="8">
+        <v>45698</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3">
         <v>98</v>
@@ -826,11 +770,11 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>27</v>
+      <c r="A11" s="8">
+        <v>45702</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3">
         <v>98</v>
@@ -849,11 +793,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>29</v>
+      <c r="A12" s="8">
+        <v>45696</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3">
         <v>98</v>
@@ -872,11 +816,11 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>31</v>
+      <c r="A13" s="8">
+        <v>45699</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>98</v>
@@ -895,11 +839,11 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
+      <c r="A14" s="8">
+        <v>45697</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3">
         <v>98</v>
@@ -918,11 +862,11 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
+      <c r="A15" s="8">
+        <v>46796</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3">
         <v>98</v>
@@ -941,11 +885,11 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>37</v>
+      <c r="A16" s="8">
+        <v>47606</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3">
         <v>98</v>
@@ -964,11 +908,11 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>39</v>
+      <c r="A17" s="8">
+        <v>45693</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3">
         <v>98</v>
@@ -987,11 +931,11 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+      <c r="A18" s="8">
+        <v>45701</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C18" s="3">
         <v>98</v>
@@ -1010,11 +954,11 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>43</v>
+      <c r="A19" s="8">
+        <v>45694</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3">
         <v>98</v>
@@ -1033,11 +977,11 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>45</v>
+      <c r="A20" s="8">
+        <v>45695</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3">
         <v>98</v>
